--- a/Data_Timbulan_Sampah/Data_Timbulan_Sampah_SIPSN_KLHK_2025.xlsx
+++ b/Data_Timbulan_Sampah/Data_Timbulan_Sampah_SIPSN_KLHK_2025.xlsx
@@ -201,8 +201,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <cols>
     <col min="1" max="1" width="6.75" customWidth="1"/>
-    <col min="2" max="2" width="10.8" customWidth="1"/>
-    <col min="3" max="3" width="24.3" customWidth="1"/>
+    <col min="2" max="2" width="35.1" customWidth="1"/>
+    <col min="3" max="3" width="43.2" customWidth="1"/>
     <col min="4" max="4" width="36.45" customWidth="1"/>
     <col min="5" max="5" width="37.800000000000004" customWidth="1"/>
   </cols>
@@ -451,6 +451,5718 @@
         <v>20440.00</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B13">
+        <is>
+          <t xml:space="preserve">Aceh</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C13">
+        <is>
+          <t xml:space="preserve">Kab. Bireuen</t>
+        </is>
+      </c>
+      <c r="D13" s="66">
+        <v>163.95</v>
+      </c>
+      <c r="E13" s="64">
+        <v>59840.29</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B14">
+        <is>
+          <t xml:space="preserve">Aceh</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C14">
+        <is>
+          <t xml:space="preserve">Kab. Aceh Barat Daya</t>
+        </is>
+      </c>
+      <c r="D14" s="66">
+        <v>80.67</v>
+      </c>
+      <c r="E14" s="64">
+        <v>29444.55</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B15">
+        <is>
+          <t xml:space="preserve">Aceh</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C15">
+        <is>
+          <t xml:space="preserve">Kab. Gayo Lues</t>
+        </is>
+      </c>
+      <c r="D15" s="66">
+        <v>41.94</v>
+      </c>
+      <c r="E15" s="64">
+        <v>15308.98</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B16">
+        <is>
+          <t xml:space="preserve">Aceh</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C16">
+        <is>
+          <t xml:space="preserve">Kab. Aceh Jaya</t>
+        </is>
+      </c>
+      <c r="D16" s="66">
+        <v>50.70</v>
+      </c>
+      <c r="E16" s="64">
+        <v>18506.78</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B17">
+        <is>
+          <t xml:space="preserve">Aceh</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C17">
+        <is>
+          <t xml:space="preserve">Kab. Nagan Raya</t>
+        </is>
+      </c>
+      <c r="D17" s="66">
+        <v>72.44</v>
+      </c>
+      <c r="E17" s="64">
+        <v>26441.04</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B18">
+        <is>
+          <t xml:space="preserve">Aceh</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C18">
+        <is>
+          <t xml:space="preserve">Kab. Aceh Tamiang</t>
+        </is>
+      </c>
+      <c r="D18" s="66">
+        <v>126.61</v>
+      </c>
+      <c r="E18" s="64">
+        <v>46213.96</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B19">
+        <is>
+          <t xml:space="preserve">Aceh</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C19">
+        <is>
+          <t xml:space="preserve">Kab. Bener Meriah</t>
+        </is>
+      </c>
+      <c r="D19" s="66">
+        <v>68.81</v>
+      </c>
+      <c r="E19" s="64">
+        <v>25117.26</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B20">
+        <is>
+          <t xml:space="preserve">Aceh</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C20">
+        <is>
+          <t xml:space="preserve">Kab. Pidie Jaya</t>
+        </is>
+      </c>
+      <c r="D20" s="66">
+        <v>84.15</v>
+      </c>
+      <c r="E20" s="64">
+        <v>30716.39</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B21">
+        <is>
+          <t xml:space="preserve">Aceh</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C21">
+        <is>
+          <t xml:space="preserve">Kota Banda Aceh</t>
+        </is>
+      </c>
+      <c r="D21" s="66">
+        <v>241.17</v>
+      </c>
+      <c r="E21" s="64">
+        <v>88025.52</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B22">
+        <is>
+          <t xml:space="preserve">Aceh</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C22">
+        <is>
+          <t xml:space="preserve">Kota Sabang</t>
+        </is>
+      </c>
+      <c r="D22" s="66">
+        <v>21.14</v>
+      </c>
+      <c r="E22" s="64">
+        <v>7716.16</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B23">
+        <is>
+          <t xml:space="preserve">Aceh</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C23">
+        <is>
+          <t xml:space="preserve">Kota Lhokseumawe</t>
+        </is>
+      </c>
+      <c r="D23" s="66">
+        <v>102.03</v>
+      </c>
+      <c r="E23" s="64">
+        <v>37239.37</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B24">
+        <is>
+          <t xml:space="preserve">Aceh</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C24">
+        <is>
+          <t xml:space="preserve">Kota Langsa</t>
+        </is>
+      </c>
+      <c r="D24" s="66">
+        <v>91.96</v>
+      </c>
+      <c r="E24" s="64">
+        <v>33564.31</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B25">
+        <is>
+          <t xml:space="preserve">Aceh</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C25">
+        <is>
+          <t xml:space="preserve">Kota Subulussalam</t>
+        </is>
+      </c>
+      <c r="D25" s="66">
+        <v>52.78</v>
+      </c>
+      <c r="E25" s="64">
+        <v>19263.42</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B26">
+        <is>
+          <t xml:space="preserve">Sumatera Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C26">
+        <is>
+          <t xml:space="preserve">Kab. Nias</t>
+        </is>
+      </c>
+      <c r="D26" s="66">
+        <v>59.39</v>
+      </c>
+      <c r="E26" s="64">
+        <v>21678.52</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B27">
+        <is>
+          <t xml:space="preserve">Sumatera Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C27">
+        <is>
+          <t xml:space="preserve">Kab. Simalungun</t>
+        </is>
+      </c>
+      <c r="D27" s="66">
+        <v>533.75</v>
+      </c>
+      <c r="E27" s="64">
+        <v>194818.57</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B28">
+        <is>
+          <t xml:space="preserve">Sumatera Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C28">
+        <is>
+          <t xml:space="preserve">Kab. Pakpak Bharat</t>
+        </is>
+      </c>
+      <c r="D28" s="66">
+        <v>22.69</v>
+      </c>
+      <c r="E28" s="64">
+        <v>8282.43</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B29">
+        <is>
+          <t xml:space="preserve">Sumatera Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C29">
+        <is>
+          <t xml:space="preserve">Kab. Humbang Hasundutan</t>
+        </is>
+      </c>
+      <c r="D29" s="66">
+        <v>62.12</v>
+      </c>
+      <c r="E29" s="64">
+        <v>22674.82</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B30">
+        <is>
+          <t xml:space="preserve">Sumatera Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C30">
+        <is>
+          <t xml:space="preserve">Kota Medan</t>
+        </is>
+      </c>
+      <c r="D30" s="64">
+        <v>1740.40</v>
+      </c>
+      <c r="E30" s="64">
+        <v>635245.31</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B31">
+        <is>
+          <t xml:space="preserve">Sumatera Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C31">
+        <is>
+          <t xml:space="preserve">Kota Tanjung Balai</t>
+        </is>
+      </c>
+      <c r="D31" s="66">
+        <v>94.03</v>
+      </c>
+      <c r="E31" s="64">
+        <v>34321.50</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B32">
+        <is>
+          <t xml:space="preserve">Sumatera Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C32">
+        <is>
+          <t xml:space="preserve">Kab. Pesisir Selatan</t>
+        </is>
+      </c>
+      <c r="D32" s="66">
+        <v>160.14</v>
+      </c>
+      <c r="E32" s="64">
+        <v>58449.57</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B33">
+        <is>
+          <t xml:space="preserve">Sumatera Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C33">
+        <is>
+          <t xml:space="preserve">Kab. Solok</t>
+        </is>
+      </c>
+      <c r="D33" s="66">
+        <v>164.17</v>
+      </c>
+      <c r="E33" s="64">
+        <v>59922.78</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B34">
+        <is>
+          <t xml:space="preserve">Sumatera Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C34">
+        <is>
+          <t xml:space="preserve">Kab. Padang Pariaman</t>
+        </is>
+      </c>
+      <c r="D34" s="66">
+        <v>22.96</v>
+      </c>
+      <c r="E34" s="64">
+        <v>8379.85</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B35">
+        <is>
+          <t xml:space="preserve">Sumatera Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C35">
+        <is>
+          <t xml:space="preserve">Kab. Agam</t>
+        </is>
+      </c>
+      <c r="D35" s="66">
+        <v>223.97</v>
+      </c>
+      <c r="E35" s="64">
+        <v>81747.84</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B36">
+        <is>
+          <t xml:space="preserve">Sumatera Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C36">
+        <is>
+          <t xml:space="preserve">Kab. Dharmasraya</t>
+        </is>
+      </c>
+      <c r="D36" s="66">
+        <v>122.02</v>
+      </c>
+      <c r="E36" s="64">
+        <v>44535.84</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B37">
+        <is>
+          <t xml:space="preserve">Sumatera Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C37">
+        <is>
+          <t xml:space="preserve">Kab. Solok Selatan</t>
+        </is>
+      </c>
+      <c r="D37" s="66">
+        <v>67.64</v>
+      </c>
+      <c r="E37" s="64">
+        <v>24687.56</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B38">
+        <is>
+          <t xml:space="preserve">Sumatera Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C38">
+        <is>
+          <t xml:space="preserve">Kota Padang</t>
+        </is>
+      </c>
+      <c r="D38" s="66">
+        <v>668.98</v>
+      </c>
+      <c r="E38" s="64">
+        <v>244179.26</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B39">
+        <is>
+          <t xml:space="preserve">Sumatera Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C39">
+        <is>
+          <t xml:space="preserve">Kota Solok</t>
+        </is>
+      </c>
+      <c r="D39" s="66">
+        <v>59.89</v>
+      </c>
+      <c r="E39" s="64">
+        <v>21858.79</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B40">
+        <is>
+          <t xml:space="preserve">Sumatera Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C40">
+        <is>
+          <t xml:space="preserve">Kota Sawahlunto</t>
+        </is>
+      </c>
+      <c r="D40" s="66">
+        <v>19.24</v>
+      </c>
+      <c r="E40" s="64">
+        <v>7024.21</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B41">
+        <is>
+          <t xml:space="preserve">Sumatera Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C41">
+        <is>
+          <t xml:space="preserve">Kota Padang Panjang</t>
+        </is>
+      </c>
+      <c r="D41" s="66">
+        <v>51.12</v>
+      </c>
+      <c r="E41" s="64">
+        <v>18657.34</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B42">
+        <is>
+          <t xml:space="preserve">Sumatera Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C42">
+        <is>
+          <t xml:space="preserve">Kota Bukittinggi</t>
+        </is>
+      </c>
+      <c r="D42" s="66">
+        <v>134.71</v>
+      </c>
+      <c r="E42" s="64">
+        <v>49170.54</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B43">
+        <is>
+          <t xml:space="preserve">Sumatera Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C43">
+        <is>
+          <t xml:space="preserve">Kota Payakumbuh</t>
+        </is>
+      </c>
+      <c r="D43" s="66">
+        <v>96.90</v>
+      </c>
+      <c r="E43" s="64">
+        <v>35368.52</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B44">
+        <is>
+          <t xml:space="preserve">Sumatera Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C44">
+        <is>
+          <t xml:space="preserve">Kota Pariaman</t>
+        </is>
+      </c>
+      <c r="D44" s="66">
+        <v>41.53</v>
+      </c>
+      <c r="E44" s="64">
+        <v>15159.91</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B45">
+        <is>
+          <t xml:space="preserve">Riau</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C45">
+        <is>
+          <t xml:space="preserve">Kab. Siak</t>
+        </is>
+      </c>
+      <c r="D45" s="66">
+        <v>198.30</v>
+      </c>
+      <c r="E45" s="64">
+        <v>72380.96</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B46">
+        <is>
+          <t xml:space="preserve">Riau</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C46">
+        <is>
+          <t xml:space="preserve">Kota Pekanbaru</t>
+        </is>
+      </c>
+      <c r="D46" s="64">
+        <v>1050.84</v>
+      </c>
+      <c r="E46" s="64">
+        <v>383556.27</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B47">
+        <is>
+          <t xml:space="preserve">Riau</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C47">
+        <is>
+          <t xml:space="preserve">Kota Dumai</t>
+        </is>
+      </c>
+      <c r="D47" s="66">
+        <v>177.63</v>
+      </c>
+      <c r="E47" s="64">
+        <v>64834.22</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B48">
+        <is>
+          <t xml:space="preserve">Jambi</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C48">
+        <is>
+          <t xml:space="preserve">Kab. Batanghari</t>
+        </is>
+      </c>
+      <c r="D48" s="66">
+        <v>128.11</v>
+      </c>
+      <c r="E48" s="64">
+        <v>46761.03</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B49">
+        <is>
+          <t xml:space="preserve">Jambi</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C49">
+        <is>
+          <t xml:space="preserve">Kota Sungai Penuh</t>
+        </is>
+      </c>
+      <c r="D49" s="66">
+        <v>51.24</v>
+      </c>
+      <c r="E49" s="64">
+        <v>18703.15</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B50">
+        <is>
+          <t xml:space="preserve">Sumatera Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C50">
+        <is>
+          <t xml:space="preserve">Kab. Ogan Komering Ulu</t>
+        </is>
+      </c>
+      <c r="D50" s="66">
+        <v>156.02</v>
+      </c>
+      <c r="E50" s="64">
+        <v>56947.01</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B51">
+        <is>
+          <t xml:space="preserve">Sumatera Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C51">
+        <is>
+          <t xml:space="preserve">Kab. Muara Enim</t>
+        </is>
+      </c>
+      <c r="D51" s="66">
+        <v>261.49</v>
+      </c>
+      <c r="E51" s="64">
+        <v>95444.73</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B52">
+        <is>
+          <t xml:space="preserve">Sumatera Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C52">
+        <is>
+          <t xml:space="preserve">Kab. Musi Banyuasin</t>
+        </is>
+      </c>
+      <c r="D52" s="66">
+        <v>288.22</v>
+      </c>
+      <c r="E52" s="64">
+        <v>105199.57</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B53">
+        <is>
+          <t xml:space="preserve">Sumatera Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C53">
+        <is>
+          <t xml:space="preserve">Kab. Ogan Komering Ulu Selatan</t>
+        </is>
+      </c>
+      <c r="D53" s="66">
+        <v>162.78</v>
+      </c>
+      <c r="E53" s="64">
+        <v>59412.95</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B54">
+        <is>
+          <t xml:space="preserve">Sumatera Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C54">
+        <is>
+          <t xml:space="preserve">Kota Pagar Alam</t>
+        </is>
+      </c>
+      <c r="D54" s="66">
+        <v>78.13</v>
+      </c>
+      <c r="E54" s="64">
+        <v>28515.63</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B55">
+        <is>
+          <t xml:space="preserve">Sumatera Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C55">
+        <is>
+          <t xml:space="preserve">Kota Prabumulih</t>
+        </is>
+      </c>
+      <c r="D55" s="66">
+        <v>102.95</v>
+      </c>
+      <c r="E55" s="64">
+        <v>37577.66</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B56">
+        <is>
+          <t xml:space="preserve">Bengkulu</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C56">
+        <is>
+          <t xml:space="preserve">Kab. Bengkulu Utara</t>
+        </is>
+      </c>
+      <c r="D56" s="66">
+        <v>187.16</v>
+      </c>
+      <c r="E56" s="64">
+        <v>68313.98</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B57">
+        <is>
+          <t xml:space="preserve">Bengkulu</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C57">
+        <is>
+          <t xml:space="preserve">Kab. Seluma</t>
+        </is>
+      </c>
+      <c r="D57" s="66">
+        <v>108.75</v>
+      </c>
+      <c r="E57" s="64">
+        <v>39695.03</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B58">
+        <is>
+          <t xml:space="preserve">Bengkulu</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C58">
+        <is>
+          <t xml:space="preserve">Kab. Lebong</t>
+        </is>
+      </c>
+      <c r="D58" s="66">
+        <v>46.21</v>
+      </c>
+      <c r="E58" s="64">
+        <v>16865.92</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B59">
+        <is>
+          <t xml:space="preserve">Bengkulu</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C59">
+        <is>
+          <t xml:space="preserve">Kab. Bengkulu Tengah</t>
+        </is>
+      </c>
+      <c r="D59" s="66">
+        <v>61.34</v>
+      </c>
+      <c r="E59" s="64">
+        <v>22387.82</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B60">
+        <is>
+          <t xml:space="preserve">Bengkulu</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C60">
+        <is>
+          <t xml:space="preserve">Kota Bengkulu</t>
+        </is>
+      </c>
+      <c r="D60" s="66">
+        <v>200.27</v>
+      </c>
+      <c r="E60" s="64">
+        <v>73097.27</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B61">
+        <is>
+          <t xml:space="preserve">Lampung</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C61">
+        <is>
+          <t xml:space="preserve">Kab. Lampung Selatan</t>
+        </is>
+      </c>
+      <c r="D61" s="66">
+        <v>780.07</v>
+      </c>
+      <c r="E61" s="64">
+        <v>284724.35</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B62">
+        <is>
+          <t xml:space="preserve">Lampung</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C62">
+        <is>
+          <t xml:space="preserve">Kab. Lampung Utara</t>
+        </is>
+      </c>
+      <c r="D62" s="66">
+        <v>270.25</v>
+      </c>
+      <c r="E62" s="64">
+        <v>98641.40</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B63">
+        <is>
+          <t xml:space="preserve">Lampung</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C63">
+        <is>
+          <t xml:space="preserve">Kab. Lampung Barat</t>
+        </is>
+      </c>
+      <c r="D63" s="66">
+        <v>127.87</v>
+      </c>
+      <c r="E63" s="64">
+        <v>46670.80</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B64">
+        <is>
+          <t xml:space="preserve">Lampung</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C64">
+        <is>
+          <t xml:space="preserve">Kab. Tulang Bawang</t>
+        </is>
+      </c>
+      <c r="D64" s="66">
+        <v>176.02</v>
+      </c>
+      <c r="E64" s="64">
+        <v>64245.84</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B65">
+        <is>
+          <t xml:space="preserve">Lampung</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C65">
+        <is>
+          <t xml:space="preserve">Kab. Tanggamus</t>
+        </is>
+      </c>
+      <c r="D65" s="66">
+        <v>375.42</v>
+      </c>
+      <c r="E65" s="64">
+        <v>137029.76</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B66">
+        <is>
+          <t xml:space="preserve">Lampung</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C66">
+        <is>
+          <t xml:space="preserve">Kab. Pesawaran</t>
+        </is>
+      </c>
+      <c r="D66" s="66">
+        <v>200.42</v>
+      </c>
+      <c r="E66" s="64">
+        <v>73152.86</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B67">
+        <is>
+          <t xml:space="preserve">Lampung</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C67">
+        <is>
+          <t xml:space="preserve">Kab. Pringsewu</t>
+        </is>
+      </c>
+      <c r="D67" s="66">
+        <v>177.93</v>
+      </c>
+      <c r="E67" s="64">
+        <v>64945.76</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B68">
+        <is>
+          <t xml:space="preserve">Lampung</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C68">
+        <is>
+          <t xml:space="preserve">Kab. Mesuji</t>
+        </is>
+      </c>
+      <c r="D68" s="66">
+        <v>97.58</v>
+      </c>
+      <c r="E68" s="64">
+        <v>35615.53</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B69">
+        <is>
+          <t xml:space="preserve">Lampung</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C69">
+        <is>
+          <t xml:space="preserve">Kab. Pesisir Barat</t>
+        </is>
+      </c>
+      <c r="D69" s="66">
+        <v>69.48</v>
+      </c>
+      <c r="E69" s="64">
+        <v>25360.20</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B70">
+        <is>
+          <t xml:space="preserve">Lampung</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C70">
+        <is>
+          <t xml:space="preserve">Kota Bandar Lampung</t>
+        </is>
+      </c>
+      <c r="D70" s="66">
+        <v>715.13</v>
+      </c>
+      <c r="E70" s="64">
+        <v>261022.21</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B71">
+        <is>
+          <t xml:space="preserve">Kepulauan Bangka Belitung</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C71">
+        <is>
+          <t xml:space="preserve">Kab. Bangka Tengah</t>
+        </is>
+      </c>
+      <c r="D71" s="66">
+        <v>116.04</v>
+      </c>
+      <c r="E71" s="64">
+        <v>42355.80</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B72">
+        <is>
+          <t xml:space="preserve">Kepulauan Bangka Belitung</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C72">
+        <is>
+          <t xml:space="preserve">Kab. Bangka Barat</t>
+        </is>
+      </c>
+      <c r="D72" s="66">
+        <v>87.61</v>
+      </c>
+      <c r="E72" s="64">
+        <v>31977.94</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B73">
+        <is>
+          <t xml:space="preserve">Kepulauan Bangka Belitung</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C73">
+        <is>
+          <t xml:space="preserve">Kab. Belitung Timur</t>
+        </is>
+      </c>
+      <c r="D73" s="66">
+        <v>53.00</v>
+      </c>
+      <c r="E73" s="64">
+        <v>19344.27</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B74">
+        <is>
+          <t xml:space="preserve">Kepulauan Riau</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C74">
+        <is>
+          <t xml:space="preserve">Kab. Bintan</t>
+        </is>
+      </c>
+      <c r="D74" s="66">
+        <v>59.53</v>
+      </c>
+      <c r="E74" s="64">
+        <v>21729.66</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B75">
+        <is>
+          <t xml:space="preserve">Kepulauan Riau</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C75">
+        <is>
+          <t xml:space="preserve">Kab. Lingga</t>
+        </is>
+      </c>
+      <c r="D75" s="66">
+        <v>50.99</v>
+      </c>
+      <c r="E75" s="64">
+        <v>18610.99</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B76">
+        <is>
+          <t xml:space="preserve">Kepulauan Riau</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C76">
+        <is>
+          <t xml:space="preserve">Kota Tanjung Pinang</t>
+        </is>
+      </c>
+      <c r="D76" s="66">
+        <v>155.97</v>
+      </c>
+      <c r="E76" s="64">
+        <v>56930.51</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B77">
+        <is>
+          <t xml:space="preserve">DKI Jakarta</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C77">
+        <is>
+          <t xml:space="preserve">Kab. Adm. Kep. Seribu</t>
+        </is>
+      </c>
+      <c r="D77" s="66">
+        <v>18.16</v>
+      </c>
+      <c r="E77" s="64">
+        <v>6627.90</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B78">
+        <is>
+          <t xml:space="preserve">DKI Jakarta</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C78">
+        <is>
+          <t xml:space="preserve">Kota Adm. Jakarta Pusat</t>
+        </is>
+      </c>
+      <c r="D78" s="66">
+        <v>858.09</v>
+      </c>
+      <c r="E78" s="64">
+        <v>313203.39</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B79">
+        <is>
+          <t xml:space="preserve">DKI Jakarta</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C79">
+        <is>
+          <t xml:space="preserve">Kota Adm. Jakarta Utara</t>
+        </is>
+      </c>
+      <c r="D79" s="64">
+        <v>1711.55</v>
+      </c>
+      <c r="E79" s="64">
+        <v>624714.06</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B80">
+        <is>
+          <t xml:space="preserve">DKI Jakarta</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C80">
+        <is>
+          <t xml:space="preserve">Kota Adm. Jakarta Barat</t>
+        </is>
+      </c>
+      <c r="D80" s="64">
+        <v>2213.61</v>
+      </c>
+      <c r="E80" s="64">
+        <v>807966.60</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B81">
+        <is>
+          <t xml:space="preserve">DKI Jakarta</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C81">
+        <is>
+          <t xml:space="preserve">Kota Adm. Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="D81" s="64">
+        <v>2005.43</v>
+      </c>
+      <c r="E81" s="64">
+        <v>731982.61</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B82">
+        <is>
+          <t xml:space="preserve">DKI Jakarta</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C82">
+        <is>
+          <t xml:space="preserve">Kota Adm. Jakarta Timur</t>
+        </is>
+      </c>
+      <c r="D82" s="64">
+        <v>2374.14</v>
+      </c>
+      <c r="E82" s="64">
+        <v>866562.58</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B83">
+        <is>
+          <t xml:space="preserve">Jawa Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C83">
+        <is>
+          <t xml:space="preserve">Kab. Bogor</t>
+        </is>
+      </c>
+      <c r="D83" s="64">
+        <v>2841.15</v>
+      </c>
+      <c r="E83" s="64">
+        <v>1037020.30</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B84">
+        <is>
+          <t xml:space="preserve">Jawa Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C84">
+        <is>
+          <t xml:space="preserve">Kab. Cianjur</t>
+        </is>
+      </c>
+      <c r="D84" s="64">
+        <v>1096.33</v>
+      </c>
+      <c r="E84" s="64">
+        <v>400161.44</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B85">
+        <is>
+          <t xml:space="preserve">Jawa Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C85">
+        <is>
+          <t xml:space="preserve">Kab. Garut</t>
+        </is>
+      </c>
+      <c r="D85" s="64">
+        <v>1160.14</v>
+      </c>
+      <c r="E85" s="64">
+        <v>423450.24</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B86">
+        <is>
+          <t xml:space="preserve">Jawa Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C86">
+        <is>
+          <t xml:space="preserve">Kab. Ciamis</t>
+        </is>
+      </c>
+      <c r="D86" s="66">
+        <v>506.53</v>
+      </c>
+      <c r="E86" s="64">
+        <v>184884.18</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B87">
+        <is>
+          <t xml:space="preserve">Jawa Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C87">
+        <is>
+          <t xml:space="preserve">Kab. Kuningan</t>
+        </is>
+      </c>
+      <c r="D87" s="66">
+        <v>499.13</v>
+      </c>
+      <c r="E87" s="64">
+        <v>182181.87</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B88">
+        <is>
+          <t xml:space="preserve">Jawa Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C88">
+        <is>
+          <t xml:space="preserve">Kab. Cirebon</t>
+        </is>
+      </c>
+      <c r="D88" s="64">
+        <v>1249.95</v>
+      </c>
+      <c r="E88" s="64">
+        <v>456230.47</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B89">
+        <is>
+          <t xml:space="preserve">Jawa Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C89">
+        <is>
+          <t xml:space="preserve">Kab. Sumedang</t>
+        </is>
+      </c>
+      <c r="D89" s="66">
+        <v>490.66</v>
+      </c>
+      <c r="E89" s="64">
+        <v>179092.36</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B90">
+        <is>
+          <t xml:space="preserve">Jawa Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C90">
+        <is>
+          <t xml:space="preserve">Kab. Indramayu</t>
+        </is>
+      </c>
+      <c r="D90" s="64">
+        <v>1148.42</v>
+      </c>
+      <c r="E90" s="64">
+        <v>419174.73</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B91">
+        <is>
+          <t xml:space="preserve">Jawa Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C91">
+        <is>
+          <t xml:space="preserve">Kab. Bekasi</t>
+        </is>
+      </c>
+      <c r="D91" s="64">
+        <v>2291.71</v>
+      </c>
+      <c r="E91" s="64">
+        <v>836473.27</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B92">
+        <is>
+          <t xml:space="preserve">Jawa Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C92">
+        <is>
+          <t xml:space="preserve">Kota Bogor</t>
+        </is>
+      </c>
+      <c r="D92" s="66">
+        <v>755.36</v>
+      </c>
+      <c r="E92" s="64">
+        <v>275707.63</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B93">
+        <is>
+          <t xml:space="preserve">Jawa Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C93">
+        <is>
+          <t xml:space="preserve">Kota Cirebon</t>
+        </is>
+      </c>
+      <c r="D93" s="66">
+        <v>216.35</v>
+      </c>
+      <c r="E93" s="64">
+        <v>78969.28</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B94">
+        <is>
+          <t xml:space="preserve">Jawa Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C94">
+        <is>
+          <t xml:space="preserve">Kota Tasikmalaya</t>
+        </is>
+      </c>
+      <c r="D94" s="66">
+        <v>334.14</v>
+      </c>
+      <c r="E94" s="64">
+        <v>121962.85</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B95">
+        <is>
+          <t xml:space="preserve">Jawa Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C95">
+        <is>
+          <t xml:space="preserve">Kota Banjar</t>
+        </is>
+      </c>
+      <c r="D95" s="66">
+        <v>87.63</v>
+      </c>
+      <c r="E95" s="64">
+        <v>31984.66</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B96">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C96">
+        <is>
+          <t xml:space="preserve">Kab. Wonosobo</t>
+        </is>
+      </c>
+      <c r="D96" s="66">
+        <v>368.20</v>
+      </c>
+      <c r="E96" s="64">
+        <v>134393.88</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B97">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C97">
+        <is>
+          <t xml:space="preserve">Kab. Boyolali</t>
+        </is>
+      </c>
+      <c r="D97" s="66">
+        <v>300.80</v>
+      </c>
+      <c r="E97" s="64">
+        <v>109791.60</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B98">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C98">
+        <is>
+          <t xml:space="preserve">Kab. Klaten</t>
+        </is>
+      </c>
+      <c r="D98" s="66">
+        <v>655.76</v>
+      </c>
+      <c r="E98" s="64">
+        <v>239352.07</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B99">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C99">
+        <is>
+          <t xml:space="preserve">Kab. Sukoharjo</t>
+        </is>
+      </c>
+      <c r="D99" s="66">
+        <v>366.96</v>
+      </c>
+      <c r="E99" s="64">
+        <v>133938.65</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B100">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C100">
+        <is>
+          <t xml:space="preserve">Kab. Wonogiri</t>
+        </is>
+      </c>
+      <c r="D100" s="66">
+        <v>349.56</v>
+      </c>
+      <c r="E100" s="64">
+        <v>127590.96</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B101">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C101">
+        <is>
+          <t xml:space="preserve">Kab. Sragen</t>
+        </is>
+      </c>
+      <c r="D101" s="66">
+        <v>602.86</v>
+      </c>
+      <c r="E101" s="64">
+        <v>220042.66</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B102">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C102">
+        <is>
+          <t xml:space="preserve">Kab. Rembang</t>
+        </is>
+      </c>
+      <c r="D102" s="66">
+        <v>272.86</v>
+      </c>
+      <c r="E102" s="64">
+        <v>99592.22</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B103">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C103">
+        <is>
+          <t xml:space="preserve">Kab. Demak</t>
+        </is>
+      </c>
+      <c r="D103" s="66">
+        <v>632.61</v>
+      </c>
+      <c r="E103" s="64">
+        <v>230903.38</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B104">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C104">
+        <is>
+          <t xml:space="preserve">Kab. Semarang</t>
+        </is>
+      </c>
+      <c r="D104" s="66">
+        <v>544.36</v>
+      </c>
+      <c r="E104" s="64">
+        <v>198693.04</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B105">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C105">
+        <is>
+          <t xml:space="preserve">Kab. Tegal</t>
+        </is>
+      </c>
+      <c r="D105" s="66">
+        <v>661.94</v>
+      </c>
+      <c r="E105" s="64">
+        <v>241609.56</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B106">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C106">
+        <is>
+          <t xml:space="preserve">Kota Magelang</t>
+        </is>
+      </c>
+      <c r="D106" s="66">
+        <v>85.21</v>
+      </c>
+      <c r="E106" s="64">
+        <v>31099.96</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B107">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C107">
+        <is>
+          <t xml:space="preserve">Kota Surakarta</t>
+        </is>
+      </c>
+      <c r="D107" s="66">
+        <v>421.48</v>
+      </c>
+      <c r="E107" s="64">
+        <v>153840.85</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B108">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C108">
+        <is>
+          <t xml:space="preserve">Kota Semarang</t>
+        </is>
+      </c>
+      <c r="D108" s="64">
+        <v>1190.46</v>
+      </c>
+      <c r="E108" s="64">
+        <v>434518.12</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B109">
+        <is>
+          <t xml:space="preserve">Daerah Istimewa Yogyakarta</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C109">
+        <is>
+          <t xml:space="preserve">Kab. Kulon Progo</t>
+        </is>
+      </c>
+      <c r="D109" s="66">
+        <v>217.16</v>
+      </c>
+      <c r="E109" s="64">
+        <v>79262.33</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B110">
+        <is>
+          <t xml:space="preserve">Daerah Istimewa Yogyakarta</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C110">
+        <is>
+          <t xml:space="preserve">Kab. Bantul</t>
+        </is>
+      </c>
+      <c r="D110" s="66">
+        <v>421.52</v>
+      </c>
+      <c r="E110" s="64">
+        <v>153853.22</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B111">
+        <is>
+          <t xml:space="preserve">Daerah Istimewa Yogyakarta</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C111">
+        <is>
+          <t xml:space="preserve">Kab. Gunungkidul</t>
+        </is>
+      </c>
+      <c r="D111" s="66">
+        <v>394.86</v>
+      </c>
+      <c r="E111" s="64">
+        <v>144124.84</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B112">
+        <is>
+          <t xml:space="preserve">Daerah Istimewa Yogyakarta</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C112">
+        <is>
+          <t xml:space="preserve">Kab. Sleman</t>
+        </is>
+      </c>
+      <c r="D112" s="66">
+        <v>585.30</v>
+      </c>
+      <c r="E112" s="64">
+        <v>213633.38</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B113">
+        <is>
+          <t xml:space="preserve">Daerah Istimewa Yogyakarta</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C113">
+        <is>
+          <t xml:space="preserve">Kota Yogyakarta</t>
+        </is>
+      </c>
+      <c r="D113" s="66">
+        <v>300.64</v>
+      </c>
+      <c r="E113" s="64">
+        <v>109733.60</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B114">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C114">
+        <is>
+          <t xml:space="preserve">Kab. Pacitan</t>
+        </is>
+      </c>
+      <c r="D114" s="66">
+        <v>300.25</v>
+      </c>
+      <c r="E114" s="64">
+        <v>109589.86</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B115">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C115">
+        <is>
+          <t xml:space="preserve">Kab. Ponorogo</t>
+        </is>
+      </c>
+      <c r="D115" s="66">
+        <v>391.60</v>
+      </c>
+      <c r="E115" s="64">
+        <v>142935.17</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B116">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C116">
+        <is>
+          <t xml:space="preserve">Kab. Trenggalek</t>
+        </is>
+      </c>
+      <c r="D116" s="66">
+        <v>301.52</v>
+      </c>
+      <c r="E116" s="64">
+        <v>110056.26</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B117">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C117">
+        <is>
+          <t xml:space="preserve">Kab. Blitar</t>
+        </is>
+      </c>
+      <c r="D117" s="66">
+        <v>416.36</v>
+      </c>
+      <c r="E117" s="64">
+        <v>151971.64</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B118">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C118">
+        <is>
+          <t xml:space="preserve">Kab. Kediri</t>
+        </is>
+      </c>
+      <c r="D118" s="66">
+        <v>676.79</v>
+      </c>
+      <c r="E118" s="64">
+        <v>247028.50</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B119">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C119">
+        <is>
+          <t xml:space="preserve">Kab. Malang</t>
+        </is>
+      </c>
+      <c r="D119" s="66">
+        <v>976.00</v>
+      </c>
+      <c r="E119" s="64">
+        <v>356238.93</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B120">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C120">
+        <is>
+          <t xml:space="preserve">Kab. Jember</t>
+        </is>
+      </c>
+      <c r="D120" s="64">
+        <v>1050.17</v>
+      </c>
+      <c r="E120" s="64">
+        <v>383312.63</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B121">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C121">
+        <is>
+          <t xml:space="preserve">Kab. Banyuwangi</t>
+        </is>
+      </c>
+      <c r="D121" s="66">
+        <v>842.14</v>
+      </c>
+      <c r="E121" s="64">
+        <v>307381.40</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B122">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C122">
+        <is>
+          <t xml:space="preserve">Kab. Bondowoso</t>
+        </is>
+      </c>
+      <c r="D122" s="66">
+        <v>317.35</v>
+      </c>
+      <c r="E122" s="64">
+        <v>115832.60</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B123">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C123">
+        <is>
+          <t xml:space="preserve">Kab. Situbondo</t>
+        </is>
+      </c>
+      <c r="D123" s="66">
+        <v>256.63</v>
+      </c>
+      <c r="E123" s="64">
+        <v>93669.45</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B124">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C124">
+        <is>
+          <t xml:space="preserve">Kab. Probolinggo</t>
+        </is>
+      </c>
+      <c r="D124" s="66">
+        <v>477.31</v>
+      </c>
+      <c r="E124" s="64">
+        <v>174217.71</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B125">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C125">
+        <is>
+          <t xml:space="preserve">Kab. Pasuruan</t>
+        </is>
+      </c>
+      <c r="D125" s="66">
+        <v>676.18</v>
+      </c>
+      <c r="E125" s="64">
+        <v>246806.14</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B126">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C126">
+        <is>
+          <t xml:space="preserve">Kab. Sidoarjo</t>
+        </is>
+      </c>
+      <c r="D126" s="66">
+        <v>892.26</v>
+      </c>
+      <c r="E126" s="64">
+        <v>325676.56</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B127">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C127">
+        <is>
+          <t xml:space="preserve">Kab. Mojokerto</t>
+        </is>
+      </c>
+      <c r="D127" s="66">
+        <v>450.90</v>
+      </c>
+      <c r="E127" s="64">
+        <v>164577.10</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B128">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C128">
+        <is>
+          <t xml:space="preserve">Kab. Jombang</t>
+        </is>
+      </c>
+      <c r="D128" s="66">
+        <v>534.39</v>
+      </c>
+      <c r="E128" s="64">
+        <v>195051.91</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B129">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C129">
+        <is>
+          <t xml:space="preserve">Kab. Nganjuk</t>
+        </is>
+      </c>
+      <c r="D129" s="66">
+        <v>459.44</v>
+      </c>
+      <c r="E129" s="64">
+        <v>167697.21</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B130">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C130">
+        <is>
+          <t xml:space="preserve">Kab. Madiun</t>
+        </is>
+      </c>
+      <c r="D130" s="66">
+        <v>295.15</v>
+      </c>
+      <c r="E130" s="64">
+        <v>107729.75</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B131">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C131">
+        <is>
+          <t xml:space="preserve">Kab. Magetan</t>
+        </is>
+      </c>
+      <c r="D131" s="66">
+        <v>277.12</v>
+      </c>
+      <c r="E131" s="64">
+        <v>101148.80</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B132">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C132">
+        <is>
+          <t xml:space="preserve">Kab. Ngawi</t>
+        </is>
+      </c>
+      <c r="D132" s="66">
+        <v>371.87</v>
+      </c>
+      <c r="E132" s="64">
+        <v>135732.85</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B133">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C133">
+        <is>
+          <t xml:space="preserve">Kab. Tuban</t>
+        </is>
+      </c>
+      <c r="D133" s="66">
+        <v>531.89</v>
+      </c>
+      <c r="E133" s="64">
+        <v>194138.51</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B134">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C134">
+        <is>
+          <t xml:space="preserve">Kab. Lamongan</t>
+        </is>
+      </c>
+      <c r="D134" s="66">
+        <v>547.00</v>
+      </c>
+      <c r="E134" s="64">
+        <v>199655.44</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B135">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C135">
+        <is>
+          <t xml:space="preserve">Kab. Bangkalan</t>
+        </is>
+      </c>
+      <c r="D135" s="66">
+        <v>422.08</v>
+      </c>
+      <c r="E135" s="64">
+        <v>154058.03</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B136">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C136">
+        <is>
+          <t xml:space="preserve">Kab. Pamekasan</t>
+        </is>
+      </c>
+      <c r="D136" s="66">
+        <v>281.00</v>
+      </c>
+      <c r="E136" s="64">
+        <v>102565.04</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B137">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C137">
+        <is>
+          <t xml:space="preserve">Kota Kediri</t>
+        </is>
+      </c>
+      <c r="D137" s="66">
+        <v>177.84</v>
+      </c>
+      <c r="E137" s="64">
+        <v>64911.66</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B138">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C138">
+        <is>
+          <t xml:space="preserve">Kota Malang</t>
+        </is>
+      </c>
+      <c r="D138" s="66">
+        <v>732.14</v>
+      </c>
+      <c r="E138" s="64">
+        <v>267230.53</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B139">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C139">
+        <is>
+          <t xml:space="preserve">Kota Probolinggo</t>
+        </is>
+      </c>
+      <c r="D139" s="66">
+        <v>122.20</v>
+      </c>
+      <c r="E139" s="64">
+        <v>44604.46</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B140">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C140">
+        <is>
+          <t xml:space="preserve">Kota Pasuruan</t>
+        </is>
+      </c>
+      <c r="D140" s="66">
+        <v>149.43</v>
+      </c>
+      <c r="E140" s="64">
+        <v>54541.33</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B141">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C141">
+        <is>
+          <t xml:space="preserve">Kota Mojokerto</t>
+        </is>
+      </c>
+      <c r="D141" s="66">
+        <v>71.14</v>
+      </c>
+      <c r="E141" s="64">
+        <v>25964.64</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B142">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C142">
+        <is>
+          <t xml:space="preserve">Kota Madiun</t>
+        </is>
+      </c>
+      <c r="D142" s="66">
+        <v>111.40</v>
+      </c>
+      <c r="E142" s="64">
+        <v>40660.71</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B143">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C143">
+        <is>
+          <t xml:space="preserve">Kota Surabaya</t>
+        </is>
+      </c>
+      <c r="D143" s="64">
+        <v>1810.81</v>
+      </c>
+      <c r="E143" s="64">
+        <v>660946.82</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B144">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C144">
+        <is>
+          <t xml:space="preserve">Kota Batu</t>
+        </is>
+      </c>
+      <c r="D144" s="66">
+        <v>122.14</v>
+      </c>
+      <c r="E144" s="64">
+        <v>44582.56</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B145">
+        <is>
+          <t xml:space="preserve">Banten</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C145">
+        <is>
+          <t xml:space="preserve">Kab. Lebak</t>
+        </is>
+      </c>
+      <c r="D145" s="66">
+        <v>620.61</v>
+      </c>
+      <c r="E145" s="64">
+        <v>226522.80</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B146">
+        <is>
+          <t xml:space="preserve">Banten</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C146">
+        <is>
+          <t xml:space="preserve">Kota Tangerang</t>
+        </is>
+      </c>
+      <c r="D146" s="64">
+        <v>1687.76</v>
+      </c>
+      <c r="E146" s="64">
+        <v>616032.52</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B147">
+        <is>
+          <t xml:space="preserve">Bali</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C147">
+        <is>
+          <t xml:space="preserve">Kab. Jembrana</t>
+        </is>
+      </c>
+      <c r="D147" s="66">
+        <v>165.44</v>
+      </c>
+      <c r="E147" s="64">
+        <v>60384.32</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B148">
+        <is>
+          <t xml:space="preserve">Bali</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C148">
+        <is>
+          <t xml:space="preserve">Kab. Badung</t>
+        </is>
+      </c>
+      <c r="D148" s="66">
+        <v>451.70</v>
+      </c>
+      <c r="E148" s="64">
+        <v>164871.08</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B149">
+        <is>
+          <t xml:space="preserve">Bali</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C149">
+        <is>
+          <t xml:space="preserve">Kab. Gianyar</t>
+        </is>
+      </c>
+      <c r="D149" s="66">
+        <v>561.00</v>
+      </c>
+      <c r="E149" s="64">
+        <v>204765.00</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B150">
+        <is>
+          <t xml:space="preserve">Bali</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C150">
+        <is>
+          <t xml:space="preserve">Kab. Klungkung</t>
+        </is>
+      </c>
+      <c r="D150" s="66">
+        <v>114.47</v>
+      </c>
+      <c r="E150" s="64">
+        <v>41782.11</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B151">
+        <is>
+          <t xml:space="preserve">Bali</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C151">
+        <is>
+          <t xml:space="preserve">Kab. Bangli</t>
+        </is>
+      </c>
+      <c r="D151" s="66">
+        <v>114.20</v>
+      </c>
+      <c r="E151" s="64">
+        <v>41683.73</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B152">
+        <is>
+          <t xml:space="preserve">Bali</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C152">
+        <is>
+          <t xml:space="preserve">Kab. Karangasem</t>
+        </is>
+      </c>
+      <c r="D152" s="66">
+        <v>291.80</v>
+      </c>
+      <c r="E152" s="64">
+        <v>106506.31</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B153">
+        <is>
+          <t xml:space="preserve">Bali</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C153">
+        <is>
+          <t xml:space="preserve">Kab. Buleleng</t>
+        </is>
+      </c>
+      <c r="D153" s="66">
+        <v>413.10</v>
+      </c>
+      <c r="E153" s="64">
+        <v>150779.68</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B154">
+        <is>
+          <t xml:space="preserve">Nusa Tenggara Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C154">
+        <is>
+          <t xml:space="preserve">Kab. Lombok Barat</t>
+        </is>
+      </c>
+      <c r="D154" s="66">
+        <v>305.10</v>
+      </c>
+      <c r="E154" s="64">
+        <v>111362.52</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B155">
+        <is>
+          <t xml:space="preserve">Nusa Tenggara Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C155">
+        <is>
+          <t xml:space="preserve">Kab. Sumbawa Barat</t>
+        </is>
+      </c>
+      <c r="D155" s="66">
+        <v>64.13</v>
+      </c>
+      <c r="E155" s="64">
+        <v>23407.74</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B156">
+        <is>
+          <t xml:space="preserve">Nusa Tenggara Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C156">
+        <is>
+          <t xml:space="preserve">Kab. Kupang</t>
+        </is>
+      </c>
+      <c r="D156" s="66">
+        <v>156.08</v>
+      </c>
+      <c r="E156" s="64">
+        <v>56970.66</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B157">
+        <is>
+          <t xml:space="preserve">Nusa Tenggara Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C157">
+        <is>
+          <t xml:space="preserve">Kab. Timor Tengah Utara</t>
+        </is>
+      </c>
+      <c r="D157" s="66">
+        <v>109.64</v>
+      </c>
+      <c r="E157" s="64">
+        <v>40019.18</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B158">
+        <is>
+          <t xml:space="preserve">Nusa Tenggara Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C158">
+        <is>
+          <t xml:space="preserve">Kab. Belu</t>
+        </is>
+      </c>
+      <c r="D158" s="66">
+        <v>92.57</v>
+      </c>
+      <c r="E158" s="64">
+        <v>33789.07</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B159">
+        <is>
+          <t xml:space="preserve">Nusa Tenggara Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C159">
+        <is>
+          <t xml:space="preserve">Kab. Alor</t>
+        </is>
+      </c>
+      <c r="D159" s="66">
+        <v>90.00</v>
+      </c>
+      <c r="E159" s="64">
+        <v>32850.00</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B160">
+        <is>
+          <t xml:space="preserve">Nusa Tenggara Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C160">
+        <is>
+          <t xml:space="preserve">Kab. Flores Timur</t>
+        </is>
+      </c>
+      <c r="D160" s="66">
+        <v>118.90</v>
+      </c>
+      <c r="E160" s="64">
+        <v>43397.04</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B161">
+        <is>
+          <t xml:space="preserve">Nusa Tenggara Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C161">
+        <is>
+          <t xml:space="preserve">Kab. Sikka</t>
+        </is>
+      </c>
+      <c r="D161" s="66">
+        <v>139.41</v>
+      </c>
+      <c r="E161" s="64">
+        <v>50884.07</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B162">
+        <is>
+          <t xml:space="preserve">Nusa Tenggara Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C162">
+        <is>
+          <t xml:space="preserve">Kab. Ende</t>
+        </is>
+      </c>
+      <c r="D162" s="66">
+        <v>112.58</v>
+      </c>
+      <c r="E162" s="64">
+        <v>41093.45</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B163">
+        <is>
+          <t xml:space="preserve">Nusa Tenggara Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C163">
+        <is>
+          <t xml:space="preserve">Kab. Ngada</t>
+        </is>
+      </c>
+      <c r="D163" s="66">
+        <v>121.86</v>
+      </c>
+      <c r="E163" s="64">
+        <v>44479.48</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B164">
+        <is>
+          <t xml:space="preserve">Nusa Tenggara Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C164">
+        <is>
+          <t xml:space="preserve">Kab. Manggarai</t>
+        </is>
+      </c>
+      <c r="D164" s="66">
+        <v>139.93</v>
+      </c>
+      <c r="E164" s="64">
+        <v>51076.06</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B165">
+        <is>
+          <t xml:space="preserve">Nusa Tenggara Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C165">
+        <is>
+          <t xml:space="preserve">Kab. Sumba Timur</t>
+        </is>
+      </c>
+      <c r="D165" s="66">
+        <v>105.91</v>
+      </c>
+      <c r="E165" s="64">
+        <v>38658.76</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B166">
+        <is>
+          <t xml:space="preserve">Nusa Tenggara Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C166">
+        <is>
+          <t xml:space="preserve">Kab. Sumba Barat</t>
+        </is>
+      </c>
+      <c r="D166" s="66">
+        <v>62.01</v>
+      </c>
+      <c r="E166" s="64">
+        <v>22631.90</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B167">
+        <is>
+          <t xml:space="preserve">Nusa Tenggara Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C167">
+        <is>
+          <t xml:space="preserve">Kab. Lembata</t>
+        </is>
+      </c>
+      <c r="D167" s="66">
+        <v>57.34</v>
+      </c>
+      <c r="E167" s="64">
+        <v>20928.37</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B168">
+        <is>
+          <t xml:space="preserve">Nusa Tenggara Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C168">
+        <is>
+          <t xml:space="preserve">Kab. Rote Ndao</t>
+        </is>
+      </c>
+      <c r="D168" s="66">
+        <v>60.21</v>
+      </c>
+      <c r="E168" s="64">
+        <v>21976.07</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B169">
+        <is>
+          <t xml:space="preserve">Nusa Tenggara Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C169">
+        <is>
+          <t xml:space="preserve">Kab. Manggarai Barat</t>
+        </is>
+      </c>
+      <c r="D169" s="66">
+        <v>147.31</v>
+      </c>
+      <c r="E169" s="64">
+        <v>53768.70</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B170">
+        <is>
+          <t xml:space="preserve">Nusa Tenggara Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C170">
+        <is>
+          <t xml:space="preserve">Kab. Nagekeo</t>
+        </is>
+      </c>
+      <c r="D170" s="66">
+        <v>65.78</v>
+      </c>
+      <c r="E170" s="64">
+        <v>24010.72</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B171">
+        <is>
+          <t xml:space="preserve">Nusa Tenggara Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C171">
+        <is>
+          <t xml:space="preserve">Kab. Sumba Tengah</t>
+        </is>
+      </c>
+      <c r="D171" s="66">
+        <v>36.94</v>
+      </c>
+      <c r="E171" s="64">
+        <v>13483.68</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B172">
+        <is>
+          <t xml:space="preserve">Nusa Tenggara Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C172">
+        <is>
+          <t xml:space="preserve">Kab. Sumba Barat Daya</t>
+        </is>
+      </c>
+      <c r="D172" s="66">
+        <v>164.39</v>
+      </c>
+      <c r="E172" s="64">
+        <v>60000.71</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B173">
+        <is>
+          <t xml:space="preserve">Nusa Tenggara Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C173">
+        <is>
+          <t xml:space="preserve">Kab. Manggarai Timur</t>
+        </is>
+      </c>
+      <c r="D173" s="66">
+        <v>99.86</v>
+      </c>
+      <c r="E173" s="64">
+        <v>36449.48</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B174">
+        <is>
+          <t xml:space="preserve">Nusa Tenggara Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C174">
+        <is>
+          <t xml:space="preserve">Kab. Sabu Raijua</t>
+        </is>
+      </c>
+      <c r="D174" s="66">
+        <v>37.91</v>
+      </c>
+      <c r="E174" s="64">
+        <v>13838.90</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B175">
+        <is>
+          <t xml:space="preserve">Nusa Tenggara Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C175">
+        <is>
+          <t xml:space="preserve">Kab. Malaka</t>
+        </is>
+      </c>
+      <c r="D175" s="66">
+        <v>77.40</v>
+      </c>
+      <c r="E175" s="64">
+        <v>28252.46</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B176">
+        <is>
+          <t xml:space="preserve">Nusa Tenggara Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C176">
+        <is>
+          <t xml:space="preserve">Kota Kupang</t>
+        </is>
+      </c>
+      <c r="D176" s="66">
+        <v>237.40</v>
+      </c>
+      <c r="E176" s="64">
+        <v>86651.18</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B177">
+        <is>
+          <t xml:space="preserve">Kalimantan Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C177">
+        <is>
+          <t xml:space="preserve">Kab. Sambas</t>
+        </is>
+      </c>
+      <c r="D177" s="66">
+        <v>394.65</v>
+      </c>
+      <c r="E177" s="64">
+        <v>144045.72</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B178">
+        <is>
+          <t xml:space="preserve">Kalimantan Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C178">
+        <is>
+          <t xml:space="preserve">Kab. Mempawah</t>
+        </is>
+      </c>
+      <c r="D178" s="66">
+        <v>94.87</v>
+      </c>
+      <c r="E178" s="64">
+        <v>34625.87</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B179">
+        <is>
+          <t xml:space="preserve">Kalimantan Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C179">
+        <is>
+          <t xml:space="preserve">Kab. Sanggau</t>
+        </is>
+      </c>
+      <c r="D179" s="66">
+        <v>257.69</v>
+      </c>
+      <c r="E179" s="64">
+        <v>94056.67</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B180">
+        <is>
+          <t xml:space="preserve">Kalimantan Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C180">
+        <is>
+          <t xml:space="preserve">Kab. Ketapang</t>
+        </is>
+      </c>
+      <c r="D180" s="66">
+        <v>299.95</v>
+      </c>
+      <c r="E180" s="64">
+        <v>109479.93</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B181">
+        <is>
+          <t xml:space="preserve">Kalimantan Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C181">
+        <is>
+          <t xml:space="preserve">Kab. Kapuas Hulu</t>
+        </is>
+      </c>
+      <c r="D181" s="66">
+        <v>138.49</v>
+      </c>
+      <c r="E181" s="64">
+        <v>50550.31</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B182">
+        <is>
+          <t xml:space="preserve">Kalimantan Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C182">
+        <is>
+          <t xml:space="preserve">Kab. Bengkayang</t>
+        </is>
+      </c>
+      <c r="D182" s="66">
+        <v>121.37</v>
+      </c>
+      <c r="E182" s="64">
+        <v>44299.61</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B183">
+        <is>
+          <t xml:space="preserve">Kalimantan Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C183">
+        <is>
+          <t xml:space="preserve">Kab. Landak</t>
+        </is>
+      </c>
+      <c r="D183" s="66">
+        <v>166.01</v>
+      </c>
+      <c r="E183" s="64">
+        <v>60594.82</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B184">
+        <is>
+          <t xml:space="preserve">Kalimantan Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C184">
+        <is>
+          <t xml:space="preserve">Kab. Kayong Utara</t>
+        </is>
+      </c>
+      <c r="D184" s="66">
+        <v>67.54</v>
+      </c>
+      <c r="E184" s="64">
+        <v>24653.38</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B185">
+        <is>
+          <t xml:space="preserve">Kalimantan Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C185">
+        <is>
+          <t xml:space="preserve">Kab. Kubu Raya</t>
+        </is>
+      </c>
+      <c r="D185" s="66">
+        <v>462.28</v>
+      </c>
+      <c r="E185" s="64">
+        <v>168732.20</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B186">
+        <is>
+          <t xml:space="preserve">Kalimantan Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C186">
+        <is>
+          <t xml:space="preserve">Kota Pontianak</t>
+        </is>
+      </c>
+      <c r="D186" s="66">
+        <v>480.21</v>
+      </c>
+      <c r="E186" s="64">
+        <v>175277.85</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B187">
+        <is>
+          <t xml:space="preserve">Kalimantan Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C187">
+        <is>
+          <t xml:space="preserve">Kota Singkawang</t>
+        </is>
+      </c>
+      <c r="D187" s="66">
+        <v>98.75</v>
+      </c>
+      <c r="E187" s="64">
+        <v>36043.46</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B188">
+        <is>
+          <t xml:space="preserve">Kalimantan Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C188">
+        <is>
+          <t xml:space="preserve">Kab. Kotawaringin Barat</t>
+        </is>
+      </c>
+      <c r="D188" s="66">
+        <v>141.40</v>
+      </c>
+      <c r="E188" s="64">
+        <v>51609.18</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B189">
+        <is>
+          <t xml:space="preserve">Kalimantan Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C189">
+        <is>
+          <t xml:space="preserve">Kab. Kotawaringin Timur</t>
+        </is>
+      </c>
+      <c r="D189" s="66">
+        <v>245.44</v>
+      </c>
+      <c r="E189" s="64">
+        <v>89584.91</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B190">
+        <is>
+          <t xml:space="preserve">Kalimantan Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C190">
+        <is>
+          <t xml:space="preserve">Kab. Kapuas</t>
+        </is>
+      </c>
+      <c r="D190" s="66">
+        <v>215.09</v>
+      </c>
+      <c r="E190" s="64">
+        <v>78507.85</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B191">
+        <is>
+          <t xml:space="preserve">Kalimantan Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C191">
+        <is>
+          <t xml:space="preserve">Kab. Barito Selatan</t>
+        </is>
+      </c>
+      <c r="D191" s="66">
+        <v>67.98</v>
+      </c>
+      <c r="E191" s="64">
+        <v>24813.80</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B192">
+        <is>
+          <t xml:space="preserve">Kalimantan Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C192">
+        <is>
+          <t xml:space="preserve">Kab. Katingan</t>
+        </is>
+      </c>
+      <c r="D192" s="66">
+        <v>72.79</v>
+      </c>
+      <c r="E192" s="64">
+        <v>26566.60</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B193">
+        <is>
+          <t xml:space="preserve">Kalimantan Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C193">
+        <is>
+          <t xml:space="preserve">Kab. Seruyan</t>
+        </is>
+      </c>
+      <c r="D193" s="66">
+        <v>87.16</v>
+      </c>
+      <c r="E193" s="64">
+        <v>31811.58</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B194">
+        <is>
+          <t xml:space="preserve">Kalimantan Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C194">
+        <is>
+          <t xml:space="preserve">Kab. Sukamara</t>
+        </is>
+      </c>
+      <c r="D194" s="66">
+        <v>26.89</v>
+      </c>
+      <c r="E194" s="64">
+        <v>9816.16</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B195">
+        <is>
+          <t xml:space="preserve">Kalimantan Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C195">
+        <is>
+          <t xml:space="preserve">Kab. Pulang Pisau</t>
+        </is>
+      </c>
+      <c r="D195" s="66">
+        <v>72.33</v>
+      </c>
+      <c r="E195" s="64">
+        <v>26401.00</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B196">
+        <is>
+          <t xml:space="preserve">Kalimantan Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C196">
+        <is>
+          <t xml:space="preserve">Kab. Murung Raya</t>
+        </is>
+      </c>
+      <c r="D196" s="66">
+        <v>62.15</v>
+      </c>
+      <c r="E196" s="64">
+        <v>22683.11</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B197">
+        <is>
+          <t xml:space="preserve">Kalimantan Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C197">
+        <is>
+          <t xml:space="preserve">Kab. Barito Timur</t>
+        </is>
+      </c>
+      <c r="D197" s="66">
+        <v>46.67</v>
+      </c>
+      <c r="E197" s="64">
+        <v>17032.94</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B198">
+        <is>
+          <t xml:space="preserve">Kalimantan Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C198">
+        <is>
+          <t xml:space="preserve">Kota Palangkaraya</t>
+        </is>
+      </c>
+      <c r="D198" s="66">
+        <v>162.30</v>
+      </c>
+      <c r="E198" s="64">
+        <v>59240.96</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B199">
+        <is>
+          <t xml:space="preserve">Kalimantan Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C199">
+        <is>
+          <t xml:space="preserve">Kab. Tanah Laut</t>
+        </is>
+      </c>
+      <c r="D199" s="66">
+        <v>147.93</v>
+      </c>
+      <c r="E199" s="64">
+        <v>53993.43</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B200">
+        <is>
+          <t xml:space="preserve">Kalimantan Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C200">
+        <is>
+          <t xml:space="preserve">Kab. Kotabaru</t>
+        </is>
+      </c>
+      <c r="D200" s="66">
+        <v>183.03</v>
+      </c>
+      <c r="E200" s="64">
+        <v>66806.99</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B201">
+        <is>
+          <t xml:space="preserve">Kalimantan Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C201">
+        <is>
+          <t xml:space="preserve">Kab. Banjar</t>
+        </is>
+      </c>
+      <c r="D201" s="66">
+        <v>357.43</v>
+      </c>
+      <c r="E201" s="64">
+        <v>130462.02</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B202">
+        <is>
+          <t xml:space="preserve">Kalimantan Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C202">
+        <is>
+          <t xml:space="preserve">Kab. Barito Kuala</t>
+        </is>
+      </c>
+      <c r="D202" s="66">
+        <v>98.94</v>
+      </c>
+      <c r="E202" s="64">
+        <v>36112.99</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B203">
+        <is>
+          <t xml:space="preserve">Kalimantan Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C203">
+        <is>
+          <t xml:space="preserve">Kab. Tapin</t>
+        </is>
+      </c>
+      <c r="D203" s="66">
+        <v>76.18</v>
+      </c>
+      <c r="E203" s="64">
+        <v>27805.70</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B204">
+        <is>
+          <t xml:space="preserve">Kalimantan Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C204">
+        <is>
+          <t xml:space="preserve">Kab. Hulu Sungai Selatan</t>
+        </is>
+      </c>
+      <c r="D204" s="66">
+        <v>110.07</v>
+      </c>
+      <c r="E204" s="64">
+        <v>40175.88</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B205">
+        <is>
+          <t xml:space="preserve">Kalimantan Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C205">
+        <is>
+          <t xml:space="preserve">Kab. Hulu Sungai Tengah</t>
+        </is>
+      </c>
+      <c r="D205" s="66">
+        <v>134.80</v>
+      </c>
+      <c r="E205" s="64">
+        <v>49201.82</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B206">
+        <is>
+          <t xml:space="preserve">Kalimantan Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C206">
+        <is>
+          <t xml:space="preserve">Kab. Hulu Sungai Utara</t>
+        </is>
+      </c>
+      <c r="D206" s="66">
+        <v>95.30</v>
+      </c>
+      <c r="E206" s="64">
+        <v>34784.50</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B207">
+        <is>
+          <t xml:space="preserve">Kalimantan Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C207">
+        <is>
+          <t xml:space="preserve">Kab. Tabalong</t>
+        </is>
+      </c>
+      <c r="D207" s="66">
+        <v>137.64</v>
+      </c>
+      <c r="E207" s="64">
+        <v>50238.92</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B208">
+        <is>
+          <t xml:space="preserve">Kalimantan Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C208">
+        <is>
+          <t xml:space="preserve">Kab. Tanah Bumbu</t>
+        </is>
+      </c>
+      <c r="D208" s="66">
+        <v>198.90</v>
+      </c>
+      <c r="E208" s="64">
+        <v>72598.74</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B209">
+        <is>
+          <t xml:space="preserve">Kalimantan Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C209">
+        <is>
+          <t xml:space="preserve">Kab. Balangan</t>
+        </is>
+      </c>
+      <c r="D209" s="66">
+        <v>59.24</v>
+      </c>
+      <c r="E209" s="64">
+        <v>21621.01</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B210">
+        <is>
+          <t xml:space="preserve">Kalimantan Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C210">
+        <is>
+          <t xml:space="preserve">Kota Banjarmasin</t>
+        </is>
+      </c>
+      <c r="D210" s="66">
+        <v>477.23</v>
+      </c>
+      <c r="E210" s="64">
+        <v>174188.15</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B211">
+        <is>
+          <t xml:space="preserve">Kalimantan Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C211">
+        <is>
+          <t xml:space="preserve">Kab. Paser</t>
+        </is>
+      </c>
+      <c r="D211" s="66">
+        <v>128.23</v>
+      </c>
+      <c r="E211" s="64">
+        <v>46805.08</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B212">
+        <is>
+          <t xml:space="preserve">Kalimantan Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C212">
+        <is>
+          <t xml:space="preserve">Kab. Kutai Kartanegara</t>
+        </is>
+      </c>
+      <c r="D212" s="66">
+        <v>395.41</v>
+      </c>
+      <c r="E212" s="64">
+        <v>144325.51</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B213">
+        <is>
+          <t xml:space="preserve">Kalimantan Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C213">
+        <is>
+          <t xml:space="preserve">Kab. Berau</t>
+        </is>
+      </c>
+      <c r="D213" s="66">
+        <v>151.72</v>
+      </c>
+      <c r="E213" s="64">
+        <v>55377.80</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B214">
+        <is>
+          <t xml:space="preserve">Kalimantan Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C214">
+        <is>
+          <t xml:space="preserve">Kab. Kutai Barat</t>
+        </is>
+      </c>
+      <c r="D214" s="66">
+        <v>70.31</v>
+      </c>
+      <c r="E214" s="64">
+        <v>25662.97</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B215">
+        <is>
+          <t xml:space="preserve">Kalimantan Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C215">
+        <is>
+          <t xml:space="preserve">Kab. Kutai Timur</t>
+        </is>
+      </c>
+      <c r="D215" s="66">
+        <v>228.17</v>
+      </c>
+      <c r="E215" s="64">
+        <v>83280.77</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B216">
+        <is>
+          <t xml:space="preserve">Kalimantan Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C216">
+        <is>
+          <t xml:space="preserve">Kab. Penajam Paser Utara</t>
+        </is>
+      </c>
+      <c r="D216" s="66">
+        <v>101.83</v>
+      </c>
+      <c r="E216" s="64">
+        <v>37168.13</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B217">
+        <is>
+          <t xml:space="preserve">Kalimantan Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C217">
+        <is>
+          <t xml:space="preserve">Kab. Mahakam Ulu</t>
+        </is>
+      </c>
+      <c r="D217" s="66">
+        <v>18.87</v>
+      </c>
+      <c r="E217" s="64">
+        <v>6888.69</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B218">
+        <is>
+          <t xml:space="preserve">Kalimantan Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C218">
+        <is>
+          <t xml:space="preserve">Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="D218" s="66">
+        <v>551.32</v>
+      </c>
+      <c r="E218" s="64">
+        <v>201230.52</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B219">
+        <is>
+          <t xml:space="preserve">Kalimantan Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C219">
+        <is>
+          <t xml:space="preserve">Kota Samarinda</t>
+        </is>
+      </c>
+      <c r="D219" s="66">
+        <v>657.26</v>
+      </c>
+      <c r="E219" s="64">
+        <v>239898.50</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B220">
+        <is>
+          <t xml:space="preserve">Kalimantan Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C220">
+        <is>
+          <t xml:space="preserve">Kota Bontang</t>
+        </is>
+      </c>
+      <c r="D220" s="66">
+        <v>108.23</v>
+      </c>
+      <c r="E220" s="64">
+        <v>39504.18</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B221">
+        <is>
+          <t xml:space="preserve">Kalimantan Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C221">
+        <is>
+          <t xml:space="preserve">Kab. Bulungan</t>
+        </is>
+      </c>
+      <c r="D221" s="66">
+        <v>86.05</v>
+      </c>
+      <c r="E221" s="64">
+        <v>31409.35</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B222">
+        <is>
+          <t xml:space="preserve">Kalimantan Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C222">
+        <is>
+          <t xml:space="preserve">Kab. Nunukan</t>
+        </is>
+      </c>
+      <c r="D222" s="66">
+        <v>45.76</v>
+      </c>
+      <c r="E222" s="64">
+        <v>16703.80</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B223">
+        <is>
+          <t xml:space="preserve">Kalimantan Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C223">
+        <is>
+          <t xml:space="preserve">Kab. Tana Tidung</t>
+        </is>
+      </c>
+      <c r="D223" s="66">
+        <v>12.13</v>
+      </c>
+      <c r="E223" s="64">
+        <v>4425.99</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B224">
+        <is>
+          <t xml:space="preserve">Sulawesi Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C224">
+        <is>
+          <t xml:space="preserve">Kab. Bolaang Mongondow</t>
+        </is>
+      </c>
+      <c r="D224" s="66">
+        <v>128.69</v>
+      </c>
+      <c r="E224" s="64">
+        <v>46971.49</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B225">
+        <is>
+          <t xml:space="preserve">Sulawesi Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C225">
+        <is>
+          <t xml:space="preserve">Kab. Minahasa</t>
+        </is>
+      </c>
+      <c r="D225" s="66">
+        <v>176.53</v>
+      </c>
+      <c r="E225" s="64">
+        <v>64432.36</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B226">
+        <is>
+          <t xml:space="preserve">Sulawesi Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C226">
+        <is>
+          <t xml:space="preserve">Kab. Kepulauan Sangihe</t>
+        </is>
+      </c>
+      <c r="D226" s="66">
+        <v>56.25</v>
+      </c>
+      <c r="E226" s="64">
+        <v>20529.64</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B227">
+        <is>
+          <t xml:space="preserve">Sulawesi Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C227">
+        <is>
+          <t xml:space="preserve">Kab. Kepulauan Talaud</t>
+        </is>
+      </c>
+      <c r="D227" s="66">
+        <v>40.15</v>
+      </c>
+      <c r="E227" s="64">
+        <v>14654.90</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B228">
+        <is>
+          <t xml:space="preserve">Sulawesi Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C228">
+        <is>
+          <t xml:space="preserve">Kab. Minahasa Selatan</t>
+        </is>
+      </c>
+      <c r="D228" s="66">
+        <v>96.52</v>
+      </c>
+      <c r="E228" s="64">
+        <v>35228.34</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B229">
+        <is>
+          <t xml:space="preserve">Sulawesi Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C229">
+        <is>
+          <t xml:space="preserve">Kab. Minahasa Utara</t>
+        </is>
+      </c>
+      <c r="D229" s="66">
+        <v>120.61</v>
+      </c>
+      <c r="E229" s="64">
+        <v>44024.29</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B230">
+        <is>
+          <t xml:space="preserve">Sulawesi Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C230">
+        <is>
+          <t xml:space="preserve">Kab. Minahasa Tenggara</t>
+        </is>
+      </c>
+      <c r="D230" s="66">
+        <v>48.53</v>
+      </c>
+      <c r="E230" s="64">
+        <v>17714.62</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B231">
+        <is>
+          <t xml:space="preserve">Sulawesi Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C231">
+        <is>
+          <t xml:space="preserve">Kab. Bolaang Mongondow Utara</t>
+        </is>
+      </c>
+      <c r="D231" s="66">
+        <v>35.20</v>
+      </c>
+      <c r="E231" s="64">
+        <v>12848.29</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B232">
+        <is>
+          <t xml:space="preserve">Sulawesi Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C232">
+        <is>
+          <t xml:space="preserve">Kab. Kep. Siau Tagulandang Biaro</t>
+        </is>
+      </c>
+      <c r="D232" s="66">
+        <v>28.21</v>
+      </c>
+      <c r="E232" s="64">
+        <v>10297.09</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B233">
+        <is>
+          <t xml:space="preserve">Sulawesi Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C233">
+        <is>
+          <t xml:space="preserve">Kab. Bolaang Mongondow Timur</t>
+        </is>
+      </c>
+      <c r="D233" s="66">
+        <v>36.54</v>
+      </c>
+      <c r="E233" s="64">
+        <v>13336.22</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B234">
+        <is>
+          <t xml:space="preserve">Sulawesi Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C234">
+        <is>
+          <t xml:space="preserve">Kab. Bolaang Mongondow Selatan</t>
+        </is>
+      </c>
+      <c r="D234" s="66">
+        <v>30.58</v>
+      </c>
+      <c r="E234" s="64">
+        <v>11162.43</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B235">
+        <is>
+          <t xml:space="preserve">Sulawesi Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C235">
+        <is>
+          <t xml:space="preserve">Kota Manado</t>
+        </is>
+      </c>
+      <c r="D235" s="66">
+        <v>296.05</v>
+      </c>
+      <c r="E235" s="64">
+        <v>108059.84</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B236">
+        <is>
+          <t xml:space="preserve">Sulawesi Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C236">
+        <is>
+          <t xml:space="preserve">Kota Bitung</t>
+        </is>
+      </c>
+      <c r="D236" s="66">
+        <v>129.62</v>
+      </c>
+      <c r="E236" s="64">
+        <v>47309.69</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B237">
+        <is>
+          <t xml:space="preserve">Sulawesi Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C237">
+        <is>
+          <t xml:space="preserve">Kota Tomohon</t>
+        </is>
+      </c>
+      <c r="D237" s="66">
+        <v>52.14</v>
+      </c>
+      <c r="E237" s="64">
+        <v>19031.10</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B238">
+        <is>
+          <t xml:space="preserve">Sulawesi Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C238">
+        <is>
+          <t xml:space="preserve">Kota Kotamobagu</t>
+        </is>
+      </c>
+      <c r="D238" s="66">
+        <v>86.65</v>
+      </c>
+      <c r="E238" s="64">
+        <v>31626.81</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B239">
+        <is>
+          <t xml:space="preserve">Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C239">
+        <is>
+          <t xml:space="preserve">Kab. Morowali</t>
+        </is>
+      </c>
+      <c r="D239" s="66">
+        <v>99.49</v>
+      </c>
+      <c r="E239" s="64">
+        <v>36314.95</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B240">
+        <is>
+          <t xml:space="preserve">Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C240">
+        <is>
+          <t xml:space="preserve">Kab. Banggai Kepulauan</t>
+        </is>
+      </c>
+      <c r="D240" s="66">
+        <v>61.71</v>
+      </c>
+      <c r="E240" s="64">
+        <v>22524.15</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B241">
+        <is>
+          <t xml:space="preserve">Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C241">
+        <is>
+          <t xml:space="preserve">Kab. Parigi Moutong</t>
+        </is>
+      </c>
+      <c r="D241" s="66">
+        <v>230.79</v>
+      </c>
+      <c r="E241" s="64">
+        <v>84237.62</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B242">
+        <is>
+          <t xml:space="preserve">Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C242">
+        <is>
+          <t xml:space="preserve">Kota Palu</t>
+        </is>
+      </c>
+      <c r="D242" s="66">
+        <v>218.43</v>
+      </c>
+      <c r="E242" s="64">
+        <v>79726.96</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B243">
+        <is>
+          <t xml:space="preserve">Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C243">
+        <is>
+          <t xml:space="preserve">Kab. Kepulauan Selayar</t>
+        </is>
+      </c>
+      <c r="D243" s="66">
+        <v>57.31</v>
+      </c>
+      <c r="E243" s="64">
+        <v>20918.15</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B244">
+        <is>
+          <t xml:space="preserve">Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C244">
+        <is>
+          <t xml:space="preserve">Kab. Bulukumba</t>
+        </is>
+      </c>
+      <c r="D244" s="66">
+        <v>192.27</v>
+      </c>
+      <c r="E244" s="64">
+        <v>70178.11</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B245">
+        <is>
+          <t xml:space="preserve">Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C245">
+        <is>
+          <t xml:space="preserve">Kab. Bantaeng</t>
+        </is>
+      </c>
+      <c r="D245" s="66">
+        <v>86.91</v>
+      </c>
+      <c r="E245" s="64">
+        <v>31720.98</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B246">
+        <is>
+          <t xml:space="preserve">Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C246">
+        <is>
+          <t xml:space="preserve">Kab. Bone</t>
+        </is>
+      </c>
+      <c r="D246" s="66">
+        <v>413.69</v>
+      </c>
+      <c r="E246" s="64">
+        <v>150995.39</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B247">
+        <is>
+          <t xml:space="preserve">Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C247">
+        <is>
+          <t xml:space="preserve">Kab. Maros</t>
+        </is>
+      </c>
+      <c r="D247" s="66">
+        <v>161.99</v>
+      </c>
+      <c r="E247" s="64">
+        <v>59126.79</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B248">
+        <is>
+          <t xml:space="preserve">Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C248">
+        <is>
+          <t xml:space="preserve">Kab. Barru</t>
+        </is>
+      </c>
+      <c r="D248" s="66">
+        <v>78.40</v>
+      </c>
+      <c r="E248" s="64">
+        <v>28616.15</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B249">
+        <is>
+          <t xml:space="preserve">Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C249">
+        <is>
+          <t xml:space="preserve">Kab. Sidenreng Rappang</t>
+        </is>
+      </c>
+      <c r="D249" s="66">
+        <v>133.28</v>
+      </c>
+      <c r="E249" s="64">
+        <v>48647.49</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B250">
+        <is>
+          <t xml:space="preserve">Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C250">
+        <is>
+          <t xml:space="preserve">Kab. Pinrang</t>
+        </is>
+      </c>
+      <c r="D250" s="66">
+        <v>191.49</v>
+      </c>
+      <c r="E250" s="64">
+        <v>69892.97</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B251">
+        <is>
+          <t xml:space="preserve">Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C251">
+        <is>
+          <t xml:space="preserve">Kab. Luwu</t>
+        </is>
+      </c>
+      <c r="D251" s="66">
+        <v>154.14</v>
+      </c>
+      <c r="E251" s="64">
+        <v>56262.71</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B252">
+        <is>
+          <t xml:space="preserve">Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C252">
+        <is>
+          <t xml:space="preserve">Kab. Tana Toraja</t>
+        </is>
+      </c>
+      <c r="D252" s="66">
+        <v>129.47</v>
+      </c>
+      <c r="E252" s="64">
+        <v>47255.46</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B253">
+        <is>
+          <t xml:space="preserve">Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C253">
+        <is>
+          <t xml:space="preserve">Kab. Luwu Utara</t>
+        </is>
+      </c>
+      <c r="D253" s="66">
+        <v>167.58</v>
+      </c>
+      <c r="E253" s="64">
+        <v>61166.88</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B254">
+        <is>
+          <t xml:space="preserve">Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C254">
+        <is>
+          <t xml:space="preserve">Kab. Luwu Timur</t>
+        </is>
+      </c>
+      <c r="D254" s="66">
+        <v>129.37</v>
+      </c>
+      <c r="E254" s="64">
+        <v>47219.61</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B255">
+        <is>
+          <t xml:space="preserve">Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C255">
+        <is>
+          <t xml:space="preserve">Kota Makassar</t>
+        </is>
+      </c>
+      <c r="D255" s="64">
+        <v>1064.06</v>
+      </c>
+      <c r="E255" s="64">
+        <v>388381.87</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B256">
+        <is>
+          <t xml:space="preserve">Sulawesi Tenggara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C256">
+        <is>
+          <t xml:space="preserve">Kab. Kolaka</t>
+        </is>
+      </c>
+      <c r="D256" s="66">
+        <v>126.29</v>
+      </c>
+      <c r="E256" s="64">
+        <v>46095.55</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B257">
+        <is>
+          <t xml:space="preserve">Sulawesi Tenggara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C257">
+        <is>
+          <t xml:space="preserve">Kab. Konawe</t>
+        </is>
+      </c>
+      <c r="D257" s="66">
+        <v>133.57</v>
+      </c>
+      <c r="E257" s="64">
+        <v>48752.87</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B258">
+        <is>
+          <t xml:space="preserve">Sulawesi Tenggara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C258">
+        <is>
+          <t xml:space="preserve">Kab. Buton</t>
+        </is>
+      </c>
+      <c r="D258" s="66">
+        <v>61.01</v>
+      </c>
+      <c r="E258" s="64">
+        <v>22269.38</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B259">
+        <is>
+          <t xml:space="preserve">Sulawesi Tenggara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C259">
+        <is>
+          <t xml:space="preserve">Kab. Konawe Utara</t>
+        </is>
+      </c>
+      <c r="D259" s="66">
+        <v>33.38</v>
+      </c>
+      <c r="E259" s="64">
+        <v>12183.55</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B260">
+        <is>
+          <t xml:space="preserve">Sulawesi Tenggara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C260">
+        <is>
+          <t xml:space="preserve">Kab. Kolaka Timur</t>
+        </is>
+      </c>
+      <c r="D260" s="66">
+        <v>64.90</v>
+      </c>
+      <c r="E260" s="64">
+        <v>23688.50</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B261">
+        <is>
+          <t xml:space="preserve">Sulawesi Tenggara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C261">
+        <is>
+          <t xml:space="preserve">Kota Kendari</t>
+        </is>
+      </c>
+      <c r="D261" s="66">
+        <v>260.32</v>
+      </c>
+      <c r="E261" s="64">
+        <v>95015.45</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B262">
+        <is>
+          <t xml:space="preserve">Gorontalo</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C262">
+        <is>
+          <t xml:space="preserve">Kab. Bone Bolango</t>
+        </is>
+      </c>
+      <c r="D262" s="66">
+        <v>52.44</v>
+      </c>
+      <c r="E262" s="64">
+        <v>19139.29</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B263">
+        <is>
+          <t xml:space="preserve">Gorontalo</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C263">
+        <is>
+          <t xml:space="preserve">Kota Gorontalo</t>
+        </is>
+      </c>
+      <c r="D263" s="66">
+        <v>143.36</v>
+      </c>
+      <c r="E263" s="64">
+        <v>52327.68</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B264">
+        <is>
+          <t xml:space="preserve">Sulawesi Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C264">
+        <is>
+          <t xml:space="preserve">Kab. Pasangkayu</t>
+        </is>
+      </c>
+      <c r="D264" s="66">
+        <v>59.95</v>
+      </c>
+      <c r="E264" s="64">
+        <v>21880.73</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B265">
+        <is>
+          <t xml:space="preserve">Sulawesi Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C265">
+        <is>
+          <t xml:space="preserve">Kab. Mamuju</t>
+        </is>
+      </c>
+      <c r="D265" s="66">
+        <v>144.19</v>
+      </c>
+      <c r="E265" s="64">
+        <v>52629.72</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B266">
+        <is>
+          <t xml:space="preserve">Sulawesi Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C266">
+        <is>
+          <t xml:space="preserve">Kab. Majene</t>
+        </is>
+      </c>
+      <c r="D266" s="66">
+        <v>108.81</v>
+      </c>
+      <c r="E266" s="64">
+        <v>39716.75</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B267">
+        <is>
+          <t xml:space="preserve">Sulawesi Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C267">
+        <is>
+          <t xml:space="preserve">Kab. Mamuju Tengah</t>
+        </is>
+      </c>
+      <c r="D267" s="66">
+        <v>143.27</v>
+      </c>
+      <c r="E267" s="64">
+        <v>52295.01</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B268">
+        <is>
+          <t xml:space="preserve">Maluku</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C268">
+        <is>
+          <t xml:space="preserve">Kab. Buru</t>
+        </is>
+      </c>
+      <c r="D268" s="66">
+        <v>63.63</v>
+      </c>
+      <c r="E268" s="64">
+        <v>23224.95</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B269">
+        <is>
+          <t xml:space="preserve">Maluku</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C269">
+        <is>
+          <t xml:space="preserve">Kab. Maluku Barat Daya</t>
+        </is>
+      </c>
+      <c r="D269" s="66">
+        <v>38.30</v>
+      </c>
+      <c r="E269" s="64">
+        <v>13978.92</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B270">
+        <is>
+          <t xml:space="preserve">Maluku</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C270">
+        <is>
+          <t xml:space="preserve">Kota Ambon</t>
+        </is>
+      </c>
+      <c r="D270" s="66">
+        <v>256.41</v>
+      </c>
+      <c r="E270" s="64">
+        <v>93589.91</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B271">
+        <is>
+          <t xml:space="preserve">Maluku Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C271">
+        <is>
+          <t xml:space="preserve">Kab. Halmahera Tengah</t>
+        </is>
+      </c>
+      <c r="D271" s="66">
+        <v>53.25</v>
+      </c>
+      <c r="E271" s="64">
+        <v>19436.25</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B272">
+        <is>
+          <t xml:space="preserve">Maluku Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C272">
+        <is>
+          <t xml:space="preserve">Kab. Halmahera Utara</t>
+        </is>
+      </c>
+      <c r="D272" s="66">
+        <v>144.36</v>
+      </c>
+      <c r="E272" s="64">
+        <v>52692.53</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B273">
+        <is>
+          <t xml:space="preserve">Maluku Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C273">
+        <is>
+          <t xml:space="preserve">Kab. Halmahera Selatan</t>
+        </is>
+      </c>
+      <c r="D273" s="66">
+        <v>129.28</v>
+      </c>
+      <c r="E273" s="64">
+        <v>47187.93</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B274">
+        <is>
+          <t xml:space="preserve">Maluku Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C274">
+        <is>
+          <t xml:space="preserve">Kab. Halmahera Timur</t>
+        </is>
+      </c>
+      <c r="D274" s="66">
+        <v>50.24</v>
+      </c>
+      <c r="E274" s="64">
+        <v>18336.32</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B275">
+        <is>
+          <t xml:space="preserve">Maluku Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C275">
+        <is>
+          <t xml:space="preserve">Kab. Pulau Morotai</t>
+        </is>
+      </c>
+      <c r="D275" s="66">
+        <v>32.74</v>
+      </c>
+      <c r="E275" s="64">
+        <v>11951.56</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B276">
+        <is>
+          <t xml:space="preserve">Papua</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C276">
+        <is>
+          <t xml:space="preserve">Kab. Keerom</t>
+        </is>
+      </c>
+      <c r="D276" s="66">
+        <v>26.03</v>
+      </c>
+      <c r="E276" s="64">
+        <v>9502.70</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B277">
+        <is>
+          <t xml:space="preserve">Papua</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C277">
+        <is>
+          <t xml:space="preserve">Kota Jayapura</t>
+        </is>
+      </c>
+      <c r="D277" s="66">
+        <v>243.04</v>
+      </c>
+      <c r="E277" s="64">
+        <v>88709.45</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B278">
+        <is>
+          <t xml:space="preserve">Papua Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C278">
+        <is>
+          <t xml:space="preserve">Kab. Manokwari</t>
+        </is>
+      </c>
+      <c r="D278" s="66">
+        <v>146.00</v>
+      </c>
+      <c r="E278" s="64">
+        <v>53290.00</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B279">
+        <is>
+          <t xml:space="preserve">Papua Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C279">
+        <is>
+          <t xml:space="preserve">Kab. Teluk Bintuni</t>
+        </is>
+      </c>
+      <c r="D279" s="66">
+        <v>36.43</v>
+      </c>
+      <c r="E279" s="64">
+        <v>13295.34</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B280">
+        <is>
+          <t xml:space="preserve">Papua Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C280">
+        <is>
+          <t xml:space="preserve">Kab. Boven Digoel</t>
+        </is>
+      </c>
+      <c r="D280" s="66">
+        <v>28.80</v>
+      </c>
+      <c r="E280" s="64">
+        <v>10511.56</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B281">
+        <is>
+          <t xml:space="preserve">Papua Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C281">
+        <is>
+          <t xml:space="preserve">Kab. Asmat</t>
+        </is>
+      </c>
+      <c r="D281" s="66">
+        <v>48.36</v>
+      </c>
+      <c r="E281" s="64">
+        <v>17651.69</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B282">
+        <is>
+          <t xml:space="preserve">Papua Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C282">
+        <is>
+          <t xml:space="preserve">Kab. Mimika</t>
+        </is>
+      </c>
+      <c r="D282" s="66">
+        <v>160.42</v>
+      </c>
+      <c r="E282" s="64">
+        <v>58553.12</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B283">
+        <is>
+          <t xml:space="preserve">Papua Barat Daya</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C283">
+        <is>
+          <t xml:space="preserve">Kab. Sorong</t>
+        </is>
+      </c>
+      <c r="D283" s="66">
+        <v>51.87</v>
+      </c>
+      <c r="E283" s="64">
+        <v>18931.67</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="65">
+        <v>2025</v>
+      </c>
+      <c t="inlineStr" r="B284">
+        <is>
+          <t xml:space="preserve">Papua Barat Daya</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C284">
+        <is>
+          <t xml:space="preserve">Kab. Tambrauw</t>
+        </is>
+      </c>
+      <c r="D284" s="66">
+        <v>16.27</v>
+      </c>
+      <c r="E284" s="64">
+        <v>5938.11</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
